--- a/history_prices/MAR/prices_20032026.xlsx
+++ b/history_prices/MAR/prices_20032026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\history_prices\MAR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20B78D5C-5640-4A50-A714-B15564591A4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{150A3DD2-4F1E-40ED-AD08-477FB0A41916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -820,7 +820,7 @@
   <cols>
     <col min="1" max="1" width="23.5703125" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="23.28515625" customWidth="1"/>
+    <col min="3" max="3" width="126" customWidth="1"/>
     <col min="4" max="4" width="23.28515625" style="4" customWidth="1"/>
     <col min="5" max="5" width="26.42578125" customWidth="1"/>
     <col min="6" max="6" width="23.28515625" customWidth="1"/>
